--- a/conformance/cases/xlsx-07-second-sheet.xlsx
+++ b/conformance/cases/xlsx-07-second-sheet.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Ghi chú" sheetId="1" r:id="rId1"/>
-    <sheet name="Luồng" sheetId="2" r:id="rId2"/>
+    <sheet name="Notes" sheetId="1" r:id="rId1"/>
+    <sheet name="Flow" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -14,7 +14,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">không phải bảng</t>
+          <t xml:space="preserve">not a table</t>
         </is>
       </c>
     </row>
@@ -104,7 +104,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bắt đầu</t>
+          <t xml:space="preserve">Start</t>
         </is>
       </c>
     </row>
@@ -121,7 +121,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">gửi yêu cầu</t>
+          <t xml:space="preserve">send request</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -148,7 +148,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xử lý</t>
+          <t xml:space="preserve">Process</t>
         </is>
       </c>
     </row>
@@ -187,7 +187,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xong</t>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
     </row>
